--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R278"/>
+  <dimension ref="A1:R280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>Items; Choice Scarf 36.649%; Mystic Water 22.073%; Life Orb 17.974%; Focus Sash 13.496%; Sitrus Berry 8.266%; Other 1.541%</t>
@@ -1283,8 +1282,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Items; Charizardite Y 100.000%</t>
@@ -1440,7 +1437,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>Items; Leftovers 83.360%; Chople Berry 3.568%; Choice Scarf 2.914%; Sitrus Berry 2.682%; Life Orb 2.283%; Magnet 1.460%; Other 3.733%</t>
@@ -3036,7 +3032,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>Items; Focus Sash 90.499%; Life Orb 3.948%; Wide Lens 1.172%; Other 4.381%</t>
@@ -3352,7 +3347,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Items; Venusaurite 100.000%</t>
@@ -4468,7 +4462,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>Items; Leftovers 97.422%; Other 2.578%</t>
@@ -5744,7 +5737,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
           <t>Items; Cameruptite 100.000%</t>
@@ -6140,7 +6132,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
           <t>Items; Glimmoranite 100.000%</t>
@@ -7016,7 +7007,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
           <t>Items; Meganiumite 100.000%</t>
@@ -10592,11 +10582,6 @@
           <t>Transform</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
         <is>
           <t>Items; Choice Scarf 50.676%; Focus Sash 24.476%; Quick Claw 5.848%; Coba Berry 4.470%; Sitrus Berry 4.330%; Leftovers 2.775%; Expert Belt 2.348%; Life Orb 2.130%; Other 2.948%</t>
@@ -15232,7 +15217,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr">
         <is>
           <t>Items; Pidgeotite 100.000%</t>
@@ -18988,7 +18972,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr">
         <is>
           <t>Items; Sharpedonite 100.000%</t>
@@ -19704,7 +19687,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr">
         <is>
           <t>Items; Sitrus Berry 97.926%; Other 2.074%</t>
@@ -22593,6 +22575,166 @@
       <c r="R278" t="inlineStr">
         <is>
           <t>Abilities; Thermal Exchange 100.000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Salamence</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Timid</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>32</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>32</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Protect 88.000%; Draco Meteor 82.000%; Hydro Pump 61.000%; Fire Blast 50.000%; Flamethrower 10.500%; Dragon Pulse 7.200%; Roost 4.100%; Other 12.000%</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Draco Meteor</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Hydro Pump</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Fire Blast</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Flamethrower</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Dragon Pulse</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Roost</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Items; Life Orb 100.000%</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>Abilities; Intimidate 100.000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Mega Salamence</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Jolly</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2</v>
+      </c>
+      <c r="D280" t="n">
+        <v>32</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>32</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Double-Edge 92.000%; Protect 85.000%; Dragon Claw 78.000%; Tailwind 55.000%; Flamethrower 12.000%; Roost 8.500%; Facade 5.200%; Other 15.000%</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Double-Edge</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Dragon Claw</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Flamethrower</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Roost</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Facade</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Items; Salamencite 100.000%</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Abilities; Aerilate 100.000%</t>
         </is>
       </c>
     </row>

--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -22689,7 +22689,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Double-Edge 92.000%; Protect 85.000%; Dragon Claw 78.000%; Tailwind 55.000%; Flamethrower 12.000%; Roost 8.500%; Facade 5.200%; Other 15.000%</t>
+          <t>Double-Edge 92.000%; Protect 85.000%; Dragon Claw 78.000%; Tailwind 55.000%; Hyper Voice 35.000%; Flamethrower 12.000%; Roost 8.500%; Giga Impact 6.000%; Facade 5.200%; Other 15.000%</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">

--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R280"/>
+  <dimension ref="A1:R284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22738,6 +22738,301 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Indeedee-M</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Timid</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>32</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="n">
+        <v>32</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Expanding Force 85.000%; Protect 75.000%; Psychic 55.000%; Dazzling Gleam 50.000%; Hyper Voice 35.000%; Shadow Ball 15.000%; Other 10.000%</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Expanding Force</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Psychic</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Dazzling Gleam</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Hyper Voice</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Shadow Ball</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Items; Life Orb 100.000%</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>Abilities; Psychic Surge 100.000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Indeedee-F</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Sassy</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>32</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>8</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>24</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Follow Me 88.000%; Expanding Force 80.000%; Protect 78.000%; Helping Hand 65.000%; Trick Room 15.000%; Imprison 8.000%; Other 6.000%</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Follow Me</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Expanding Force</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Helping Hand</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Trick Room</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Imprison</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Items; Rocky Helmet 100.000%</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>Abilities; Psychic Surge 100.000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Golisopod</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Adamant</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>20</v>
+      </c>
+      <c r="D283" t="n">
+        <v>20</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>12</v>
+      </c>
+      <c r="H283" t="n">
+        <v>12</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>First Impression 90.000%; Protect 75.000%; Liquidation 70.000%; Sucker Punch 40.000%; Leech Life 20.000%; Spikes 10.000%; Other 10.000%</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>First Impression</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Liquidation</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Sucker Punch</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Leech Life</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Spikes</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Items; Assault Vest 55.000%; Sitrus Berry 25.000%; Rocky Helmet 20.000%</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Abilities; Emergency Exit 100.000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Mega Golisopod</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Adamant</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2</v>
+      </c>
+      <c r="D284" t="n">
+        <v>32</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>32</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>First Impression 88.000%; Protect 78.000%; Iron Head 70.000%; Close Combat 55.000%; Liquidation 15.000%; Other 10.000%</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>First Impression</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Iron Head</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Close Combat</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Liquidation</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Items; Golisopite 100.000%</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>Abilities; Tough Claws 100.000%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -22844,7 +22844,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Follow Me 88.000%; Expanding Force 80.000%; Protect 78.000%; Helping Hand 65.000%; Trick Room 15.000%; Imprison 8.000%; Other 6.000%</t>
+          <t>Follow Me 88.000%; Protect 78.000%; Trick Room 70.000%; Helping Hand 65.000%; Imprison 8.000%; Other 6.000%</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -22854,12 +22854,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Expanding Force</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Trick Room</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22868,11 +22868,6 @@
         </is>
       </c>
       <c r="N282" t="inlineStr">
-        <is>
-          <t>Trick Room</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
         <is>
           <t>Imprison</t>
         </is>

--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -22844,7 +22844,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Follow Me 88.000%; Protect 78.000%; Trick Room 70.000%; Helping Hand 65.000%; Imprison 8.000%; Other 6.000%</t>
+          <t>Follow Me 88.000%; Psychic 72.000%; Trick Room 70.000%; Helping Hand 65.000%; Protect 40.000%; Imprison 8.000%; Other 6.000%</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -22868,6 +22868,11 @@
         </is>
       </c>
       <c r="N282" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
         <is>
           <t>Imprison</t>
         </is>

--- a/data/mbsmogon.xlsx
+++ b/data/mbsmogon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R284"/>
+  <dimension ref="A1:R285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23033,6 +23033,71 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Pawmot</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Jolly</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2</v>
+      </c>
+      <c r="D285" t="n">
+        <v>32</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>32</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Fake Out 100.000%; Close Combat 100.000%; Ice Punch 100.000%; Double Shock 100.000%</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Fake Out</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Close Combat</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Ice Punch</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Double Shock</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Items; Life Orb 100.000%</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>Abilities; Iron Fist 100.000%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
